--- a/bills/Jizhangxiaobangshou/-5583160835/a730b180e8d9389033e29f24d127b0465e5f0c42454793038e95ba4e14cd4e47/bill-current.xlsx
+++ b/bills/Jizhangxiaobangshou/-5583160835/a730b180e8d9389033e29f24d127b0465e5f0c42454793038e95ba4e14cd4e47/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 15:08:28</t>
+          <t>07/25 11:57:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2344.6</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2344.6</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2344.6</t>
         </is>
       </c>
     </row>
